--- a/src/app/engine/prezzi_vainieri_2026.xlsx
+++ b/src/app/engine/prezzi_vainieri_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Stefano\Controllo_fatture_vainieri\progetto_fatture\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\commerciale03\Desktop\APP\src\app\engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15978D6-CABE-4FFA-92FA-62DF8831E4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5567B12-BCD6-407A-BF32-3263D312CF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="5" xr2:uid="{2055FF45-0695-4B33-B4C8-1D44C4CA0355}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{2055FF45-0695-4B33-B4C8-1D44C4CA0355}"/>
   </bookViews>
   <sheets>
     <sheet name="FR" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
   <si>
     <t>A</t>
   </si>
@@ -90,6 +90,18 @@
   </si>
   <si>
     <t>Tutto il Paese</t>
+  </si>
+  <si>
+    <t>AL-BR-CM-CR-CT-DA-E-EC-EN-GU-IG-HA-HP-KT-LU-ME-N-NW-RG-RH-RM-SE-SL-SM-SS-SW-TN-TW-UB-W-WC-WD</t>
+  </si>
+  <si>
+    <t>B-BA-BB-BD-BH-BL-BDT-EX-CF-HR-LD-LL-NP-PL-TQ-SA-SY-TA-TRN-BS-CB-CH-CO-CV-CW-DE-DN-DY-FY-GL-HD-HG-HU-HX-L-LE-LN-LS-IP-M-MK-NG-NN-NR-OL-OX-PE-PO-PR-S-SG-SK-SN-SO-SP-ST-TF-YO-WA-WF-WN-WR-WS-WV</t>
+  </si>
+  <si>
+    <t>DT-EX-CF-HR-LD-LL-NP-PL-TQ-SA-SY-TA-TR</t>
+  </si>
+  <si>
+    <t>AB-CA-DD-DG-DH-DL-EH-FK-G-IV-KA-KY-KW-LA-ML-NE-PA-PH-SR-TD-TS</t>
   </si>
 </sst>
 </file>
@@ -545,32 +557,32 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
+      <c r="B4" t="s">
+        <v>22</v>
       </c>
       <c r="C4">
-        <v>92</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -578,10 +590,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>99</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
